--- a/internal_doc/05.测试设计/story/Sequence&AutoIncrement/基本操作.xlsx
+++ b/internal_doc/05.测试设计/story/Sequence&AutoIncrement/基本操作.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="88">
   <si>
     <t>name</t>
   </si>
@@ -386,6 +386,56 @@
   <si>
     <t>1.事务回滚成功，集合1及集合2中的记录均被回滚
 2.记录插入成功，集合1及集合2中记录的自增字段值正确(在步骤1的基础上递增，事务中自增字段值不会回滚)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新记录，自增字段值保留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合中已存在自增字段且存在记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用replace更新符更新记录，覆盖：更新前记录无自增字段、更新前记录存在自增字段
+2.使用其他操作符更新记录，覆盖：更新其他字段、记录新增自增字段、记录删除自增字段、更新自增字段值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.记录更新成功，更新记录不会修改自增字段
+2.记录更新成功，更新记录系统不会生成自增字段值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自增字段同时是shardKey时，更新记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.删除记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.记录删除成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>truncate集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.truncate集合
+2.连本coord插入记录
+3.连其他coord插入记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.集合truncate成功，检查自增字段属性值CurrentValue值为StartValue
+2.本地coord的sequence缓存被清空，重新从catalog获取新的序列值插入记录
+3.其他coord的sequence缓存被清空，重新从catalog获取新的序列值插入记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -425,7 +475,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -433,42 +483,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -484,21 +503,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -596,8 +600,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I23" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I27" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I27"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -916,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -1037,7 +1041,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="27">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1063,7 +1067,7 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1169,7 +1173,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="27">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1193,10 +1197,10 @@
       <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="J10" s="11"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="81">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="1">
@@ -1217,7 +1221,7 @@
       <c r="I11" s="1">
         <v>2</v>
       </c>
-      <c r="J11" s="11"/>
+      <c r="J11" s="6"/>
     </row>
     <row r="12" spans="1:10" ht="81">
       <c r="A12" s="1" t="s">
@@ -1294,7 +1298,7 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="81">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D15" s="1">
@@ -1317,7 +1321,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="94.5">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B16" s="5"/>
@@ -1342,7 +1346,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="54">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B17" s="5"/>
@@ -1367,7 +1371,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="54">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="5"/>
@@ -1446,7 +1450,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="175.5">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="8" t="s">
         <v>67</v>
       </c>
       <c r="B21" s="5"/>
@@ -1526,36 +1530,112 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="3"/>
-      <c r="B24" s="5"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="2"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="3"/>
+    <row r="24" spans="1:9" ht="54">
+      <c r="A24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="54">
+      <c r="A25" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="10"/>
+      <c r="C25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="27">
+      <c r="A26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="81">
+      <c r="A27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
